--- a/output/pdf_financials_xlsx/CGM.xlsx
+++ b/output/pdf_financials_xlsx/CGM.xlsx
@@ -6009,52 +6009,52 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.671195</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.405755</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.704994</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.066418</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>3.460335</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.679169</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.652129</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.163382</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.993524</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.993524</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.939498</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>5.995385</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.995385</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.995385</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>5.995385</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>5.995385</v>
       </c>
     </row>
     <row r="93">
@@ -9558,7 +9558,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -10314,7 +10318,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -10890,7 +10898,11 @@
           <t>Reserves (Note 6)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -11722,7 +11734,11 @@
           <t>Reserves (Note 6) 5,995,385</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -12404,7 +12420,11 @@
           <t>Reserves (Note 6) 657,109</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -13184,7 +13204,11 @@
           <t>Reserves (Note 8) 1,939,498</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -14228,7 +14252,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -15158,7 +15186,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -15822,7 +15854,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -16666,7 +16702,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>1.671195</v>
       </c>

--- a/output/pdf_financials_xlsx/CGM.xlsx
+++ b/output/pdf_financials_xlsx/CGM.xlsx
@@ -2597,52 +2597,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.301588</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.804042</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.06417299999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.009216999999999999</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.005421</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.015114</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001507</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.005119</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.337942</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.337942</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.016799</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.009249</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.028475</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.760705</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.515871</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.232532</v>
       </c>
     </row>
     <row r="35">
@@ -2707,52 +2707,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.301588</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.804042</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.06417299999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.009216999999999999</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>3.38359</v>
+        <v>3.389011</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.688811</v>
+        <v>0.703925</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001507</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.005119</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.337942</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.337942</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.016799</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.009249</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.012667</v>
+        <v>0.041142</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.004667</v>
+        <v>0.7653720000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.029167</v>
+        <v>0.545038</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.020833</v>
+        <v>0.253365</v>
       </c>
     </row>
     <row r="37">
@@ -3367,52 +3367,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.369086</v>
+        <v>0.067498</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.06869</v>
+        <v>0.264648</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.209899</v>
+        <v>0.145726</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.098383</v>
+        <v>0.089166</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.045398</v>
+        <v>0.039977</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.023642</v>
+        <v>0.008528000000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.009808000000000001</v>
+        <v>0.008300999999999999</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.02091</v>
+        <v>0.015791</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.693412</v>
+        <v>0.35547</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.693412</v>
+        <v>0.35547</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.028553</v>
+        <v>0.011754</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.009249</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.028475</v>
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.770705</v>
+        <v>0.01</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.526797</v>
+        <v>0.010926</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.499451</v>
+        <v>0.266919</v>
       </c>
     </row>
     <row r="49">
@@ -9042,7 +9042,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
